--- a/public/templates/forms/A-031-GovernanceReportingCalendar-FORM.xlsx
+++ b/public/templates/forms/A-031-GovernanceReportingCalendar-FORM.xlsx
@@ -298,7 +298,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -667,12 +667,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>

--- a/public/templates/forms/A-031-GovernanceReportingCalendar-FORM.xlsx
+++ b/public/templates/forms/A-031-GovernanceReportingCalendar-FORM.xlsx
@@ -5,13 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Column Instructions" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -291,8 +291,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -463,7 +464,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -551,6 +552,10 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -802,7 +807,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -923,7 +928,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="34.7" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>18</v>
       </c>
@@ -946,7 +951,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="34.7" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
@@ -1015,7 +1020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="34.7" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>33</v>
       </c>
@@ -1061,7 +1066,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="34.7" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>38</v>
       </c>
@@ -1101,7 +1106,6 @@
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">COUNTA(A11:A17)</f>
-        <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1110,7 +1114,6 @@
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">COUNTIF(G11:G17,"Overdue")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1119,7 +1122,6 @@
       </c>
       <c r="C22" s="10" t="n">
         <f aca="true">COUNTIF(F11:F17,"&lt;"&amp;TODAY())</f>
-        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1315,15 +1317,19 @@
     <mergeCell ref="A38:G38"/>
     <mergeCell ref="A42:G42"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G11:G47" type="list">
       <formula1>"On track,Due soon,Overdue,Complete"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="B11:B17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Frequency" prompt="Select a value" type="list">
+      <formula1>"Monthly,Quarterly,Semi-annually,Annually"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1334,7 +1340,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -1411,7 +1417,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="34.7" customHeight="1">
       <c r="A8" s="18" t="s">
         <v>13</v>
       </c>
@@ -1449,8 +1455,8 @@
       <c r="C10" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>84</v>
+      <c r="D10" s="23">
+        <v>46082</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1463,8 +1469,8 @@
       <c r="C11" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>86</v>
+      <c r="D11" s="23">
+        <v>46174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1557,7 +1563,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
